--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_034.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_034.xlsx
@@ -2769,7 +2769,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92">
@@ -2792,7 +2792,7 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93">
@@ -2815,7 +2815,7 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94">
@@ -2838,7 +2838,7 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95">
@@ -2861,7 +2861,7 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96">
@@ -2884,7 +2884,7 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97">
@@ -2907,7 +2907,7 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98">
@@ -2930,7 +2930,7 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99">
@@ -2953,7 +2953,7 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100">
@@ -2976,7 +2976,7 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101">
@@ -2999,7 +2999,7 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102">
